--- a/AlertPro-Pricing-Template-v2.xlsx
+++ b/AlertPro-Pricing-Template-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13472DE5-94C9-457B-80E4-6FFFE0CF263A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F496D6-1644-4AAD-A882-5126D3716B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -557,36 +557,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -903,7 +903,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="25"/>
@@ -917,7 +917,7 @@
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="25"/>
@@ -962,7 +962,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="30" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="25"/>
@@ -1001,28 +1001,28 @@
         <v>850</v>
       </c>
       <c r="C7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="D7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="E7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="F7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="G7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="H7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="I7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="J7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1122,7 +1122,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="33" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="25"/>
@@ -1200,7 +1200,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="34" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="25"/>
@@ -1235,31 +1235,31 @@
       <c r="C15" s="25"/>
       <c r="D15" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="E15" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="F15" s="12">
         <f>ROUND(F7+F8+F9+F12+F14,2)</f>
-        <v>1088.3</v>
+        <v>988.3</v>
       </c>
       <c r="G15" s="12">
         <f>ROUND(G7+G8+G9+G12+G14,2)</f>
-        <v>1088.3</v>
+        <v>988.3</v>
       </c>
       <c r="H15" s="12">
         <f>ROUND(H7+H8+H9+H10+H12+H14,2)</f>
-        <v>1172.69</v>
+        <v>1072.69</v>
       </c>
       <c r="I15" s="12">
         <f>ROUND(I7+I8+I9+I10+I12+I14,2)</f>
-        <v>1172.69</v>
+        <v>1072.69</v>
       </c>
       <c r="J15" s="12">
         <f>ROUND(J7+J8+J9+J12+J14,2)</f>
-        <v>1063.3</v>
+        <v>963.3</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1270,31 +1270,31 @@
       <c r="C16" s="25"/>
       <c r="D16" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="E16" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="F16" s="12">
         <f>ROUND(F7+F8+F9+F13+F14,2)</f>
-        <v>1296.8499999999999</v>
+        <v>1196.8499999999999</v>
       </c>
       <c r="G16" s="12">
         <f>ROUND(G7+G8+G9+G13+G14,2)</f>
-        <v>1296.8499999999999</v>
+        <v>1196.8499999999999</v>
       </c>
       <c r="H16" s="12">
         <f>ROUND(H7+H8+H9+H10+H13+H14,2)</f>
-        <v>1381.24</v>
+        <v>1281.24</v>
       </c>
       <c r="I16" s="12">
         <f>ROUND(I7+I8+I9+I10+I13+I14,2)</f>
-        <v>1381.24</v>
+        <v>1281.24</v>
       </c>
       <c r="J16" s="12">
         <f>ROUND(J7+J8+J9+J13+J14,2)</f>
-        <v>1271.8499999999999</v>
+        <v>1171.8499999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1305,31 +1305,31 @@
       <c r="C17" s="25"/>
       <c r="D17" s="12">
         <f t="shared" ref="D17:J18" si="0">ROUND(D15*0.13,2)</f>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="E17" s="12">
         <f t="shared" si="0"/>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="0"/>
-        <v>141.47999999999999</v>
+        <v>128.47999999999999</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>141.47999999999999</v>
+        <v>128.47999999999999</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>152.44999999999999</v>
+        <v>139.44999999999999</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" si="0"/>
-        <v>152.44999999999999</v>
+        <v>139.44999999999999</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>138.22999999999999</v>
+        <v>125.23</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1340,106 +1340,106 @@
       <c r="C18" s="25"/>
       <c r="D18" s="12">
         <f t="shared" si="0"/>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="E18" s="12">
         <f t="shared" si="0"/>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="0"/>
-        <v>168.59</v>
+        <v>155.59</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="0"/>
-        <v>168.59</v>
+        <v>155.59</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>179.56</v>
+        <v>166.56</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" si="0"/>
-        <v>179.56</v>
+        <v>166.56</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>165.34</v>
+        <v>152.34</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="26" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
       <c r="D19" s="13">
         <f t="shared" ref="D19:J19" si="1">D15+D17</f>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="E19" s="13">
         <f t="shared" si="1"/>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="1"/>
-        <v>1229.78</v>
+        <v>1116.78</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="1"/>
-        <v>1229.78</v>
+        <v>1116.78</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>1325.14</v>
+        <v>1212.1400000000001</v>
       </c>
       <c r="I19" s="13">
         <f t="shared" si="1"/>
-        <v>1325.14</v>
+        <v>1212.1400000000001</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v>1201.53</v>
+        <v>1088.53</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="32" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="25"/>
       <c r="D20" s="14">
         <f>D19</f>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="E20" s="14">
         <f>E19</f>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="F20" s="14">
         <f>F16+F18</f>
-        <v>1465.4399999999998</v>
+        <v>1352.4399999999998</v>
       </c>
       <c r="G20" s="14">
         <f>G16+G18</f>
-        <v>1465.4399999999998</v>
+        <v>1352.4399999999998</v>
       </c>
       <c r="H20" s="14">
         <f>H16+H18</f>
-        <v>1560.8</v>
+        <v>1447.8</v>
       </c>
       <c r="I20" s="14">
         <f>I16+I18</f>
-        <v>1560.8</v>
+        <v>1447.8</v>
       </c>
       <c r="J20" s="14">
         <f>J16+J18</f>
-        <v>1437.1899999999998</v>
+        <v>1324.1899999999998</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="30" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="25"/>
@@ -1465,7 +1465,7 @@
       <c r="J23" s="6"/>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="28" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="25"/>
@@ -1493,7 +1493,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="28" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="25"/>
@@ -1521,7 +1521,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="28" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="25"/>
@@ -1549,78 +1549,78 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="26" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="13">
         <f t="shared" ref="D27:J27" si="2">ROUND(D24*D25+D26-D19,2)</f>
-        <v>243.78</v>
+        <v>356.78</v>
       </c>
       <c r="E27" s="13">
         <f t="shared" si="2"/>
-        <v>58.78</v>
+        <v>171.78</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="2"/>
-        <v>449.22</v>
+        <v>562.22</v>
       </c>
       <c r="G27" s="13">
         <f t="shared" si="2"/>
-        <v>219.22</v>
+        <v>332.22</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="2"/>
-        <v>585.86</v>
+        <v>698.86</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="2"/>
-        <v>313.86</v>
+        <v>426.86</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="2"/>
-        <v>52.47</v>
+        <v>165.47</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="32" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
       <c r="D28" s="14">
         <f t="shared" ref="D28:J28" si="3">ROUND(D24*D25+D26-D20,2)</f>
-        <v>243.78</v>
+        <v>356.78</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="3"/>
-        <v>58.78</v>
+        <v>171.78</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>213.56</v>
+        <v>326.56</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="3"/>
-        <v>-16.440000000000001</v>
+        <v>96.56</v>
       </c>
       <c r="H28" s="14">
         <f t="shared" si="3"/>
-        <v>350.2</v>
+        <v>463.2</v>
       </c>
       <c r="I28" s="14">
         <f t="shared" si="3"/>
-        <v>78.2</v>
+        <v>191.2</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="3"/>
-        <v>-183.19</v>
+        <v>-70.19</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="30" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="25"/>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="58" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="59" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="31" t="s">
         <v>75</v>
       </c>
       <c r="B59" s="25"/>
@@ -2180,12 +2180,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A59:J59"/>
@@ -2193,12 +2187,18 @@
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A5:J5"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AlertPro-Pricing-Template-v2.xlsx
+++ b/AlertPro-Pricing-Template-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F496D6-1644-4AAD-A882-5126D3716B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0D8285-67D3-435B-9D8A-128135788821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1001,28 +1001,28 @@
         <v>850</v>
       </c>
       <c r="C7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="D7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="E7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="F7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="G7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="H7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="I7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="J7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1235,31 +1235,31 @@
       <c r="C15" s="25"/>
       <c r="D15" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="E15" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="F15" s="12">
         <f>ROUND(F7+F8+F9+F12+F14,2)</f>
-        <v>988.3</v>
+        <v>1088.3</v>
       </c>
       <c r="G15" s="12">
         <f>ROUND(G7+G8+G9+G12+G14,2)</f>
-        <v>988.3</v>
+        <v>1088.3</v>
       </c>
       <c r="H15" s="12">
         <f>ROUND(H7+H8+H9+H10+H12+H14,2)</f>
-        <v>1072.69</v>
+        <v>1172.69</v>
       </c>
       <c r="I15" s="12">
         <f>ROUND(I7+I8+I9+I10+I12+I14,2)</f>
-        <v>1072.69</v>
+        <v>1172.69</v>
       </c>
       <c r="J15" s="12">
         <f>ROUND(J7+J8+J9+J12+J14,2)</f>
-        <v>963.3</v>
+        <v>1063.3</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1270,31 +1270,31 @@
       <c r="C16" s="25"/>
       <c r="D16" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="E16" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="F16" s="12">
         <f>ROUND(F7+F8+F9+F13+F14,2)</f>
-        <v>1196.8499999999999</v>
+        <v>1296.8499999999999</v>
       </c>
       <c r="G16" s="12">
         <f>ROUND(G7+G8+G9+G13+G14,2)</f>
-        <v>1196.8499999999999</v>
+        <v>1296.8499999999999</v>
       </c>
       <c r="H16" s="12">
         <f>ROUND(H7+H8+H9+H10+H13+H14,2)</f>
-        <v>1281.24</v>
+        <v>1381.24</v>
       </c>
       <c r="I16" s="12">
         <f>ROUND(I7+I8+I9+I10+I13+I14,2)</f>
-        <v>1281.24</v>
+        <v>1381.24</v>
       </c>
       <c r="J16" s="12">
         <f>ROUND(J7+J8+J9+J13+J14,2)</f>
-        <v>1171.8499999999999</v>
+        <v>1271.8499999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1305,31 +1305,31 @@
       <c r="C17" s="25"/>
       <c r="D17" s="12">
         <f t="shared" ref="D17:J18" si="0">ROUND(D15*0.13,2)</f>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="E17" s="12">
         <f t="shared" si="0"/>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="0"/>
-        <v>128.47999999999999</v>
+        <v>141.47999999999999</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>128.47999999999999</v>
+        <v>141.47999999999999</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>139.44999999999999</v>
+        <v>152.44999999999999</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" si="0"/>
-        <v>139.44999999999999</v>
+        <v>152.44999999999999</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>125.23</v>
+        <v>138.22999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1340,31 +1340,31 @@
       <c r="C18" s="25"/>
       <c r="D18" s="12">
         <f t="shared" si="0"/>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="E18" s="12">
         <f t="shared" si="0"/>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="0"/>
-        <v>155.59</v>
+        <v>168.59</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="0"/>
-        <v>155.59</v>
+        <v>168.59</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>166.56</v>
+        <v>179.56</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" si="0"/>
-        <v>166.56</v>
+        <v>179.56</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>152.34</v>
+        <v>165.34</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1375,31 +1375,31 @@
       <c r="C19" s="25"/>
       <c r="D19" s="13">
         <f t="shared" ref="D19:J19" si="1">D15+D17</f>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="E19" s="13">
         <f t="shared" si="1"/>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="1"/>
-        <v>1116.78</v>
+        <v>1229.78</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="1"/>
-        <v>1116.78</v>
+        <v>1229.78</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>1212.1400000000001</v>
+        <v>1325.14</v>
       </c>
       <c r="I19" s="13">
         <f t="shared" si="1"/>
-        <v>1212.1400000000001</v>
+        <v>1325.14</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v>1088.53</v>
+        <v>1201.53</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1410,31 +1410,31 @@
       <c r="C20" s="25"/>
       <c r="D20" s="14">
         <f>D19</f>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="E20" s="14">
         <f>E19</f>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="F20" s="14">
         <f>F16+F18</f>
-        <v>1352.4399999999998</v>
+        <v>1465.4399999999998</v>
       </c>
       <c r="G20" s="14">
         <f>G16+G18</f>
-        <v>1352.4399999999998</v>
+        <v>1465.4399999999998</v>
       </c>
       <c r="H20" s="14">
         <f>H16+H18</f>
-        <v>1447.8</v>
+        <v>1560.8</v>
       </c>
       <c r="I20" s="14">
         <f>I16+I18</f>
-        <v>1447.8</v>
+        <v>1560.8</v>
       </c>
       <c r="J20" s="14">
         <f>J16+J18</f>
-        <v>1324.1899999999998</v>
+        <v>1437.1899999999998</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1556,31 +1556,31 @@
       <c r="C27" s="25"/>
       <c r="D27" s="13">
         <f t="shared" ref="D27:J27" si="2">ROUND(D24*D25+D26-D19,2)</f>
-        <v>356.78</v>
+        <v>243.78</v>
       </c>
       <c r="E27" s="13">
         <f t="shared" si="2"/>
-        <v>171.78</v>
+        <v>58.78</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="2"/>
-        <v>562.22</v>
+        <v>449.22</v>
       </c>
       <c r="G27" s="13">
         <f t="shared" si="2"/>
-        <v>332.22</v>
+        <v>219.22</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="2"/>
-        <v>698.86</v>
+        <v>585.86</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="2"/>
-        <v>426.86</v>
+        <v>313.86</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="2"/>
-        <v>165.47</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1591,31 +1591,31 @@
       <c r="C28" s="25"/>
       <c r="D28" s="14">
         <f t="shared" ref="D28:J28" si="3">ROUND(D24*D25+D26-D20,2)</f>
-        <v>356.78</v>
+        <v>243.78</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="3"/>
-        <v>171.78</v>
+        <v>58.78</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>326.56</v>
+        <v>213.56</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="3"/>
-        <v>96.56</v>
+        <v>-16.440000000000001</v>
       </c>
       <c r="H28" s="14">
         <f t="shared" si="3"/>
-        <v>463.2</v>
+        <v>350.2</v>
       </c>
       <c r="I28" s="14">
         <f t="shared" si="3"/>
-        <v>191.2</v>
+        <v>78.2</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="3"/>
-        <v>-70.19</v>
+        <v>-183.19</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/AlertPro-Pricing-Template-v2.xlsx
+++ b/AlertPro-Pricing-Template-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0D8285-67D3-435B-9D8A-128135788821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50986D0-06B0-467E-ADB6-74EAB5DFBCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1001,28 +1001,28 @@
         <v>850</v>
       </c>
       <c r="C7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="D7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="E7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="F7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="G7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="H7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="I7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
       <c r="J7" s="9">
-        <v>533.25</v>
+        <v>433.25</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1235,31 +1235,31 @@
       <c r="C15" s="25"/>
       <c r="D15" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="E15" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="F15" s="12">
         <f>ROUND(F7+F8+F9+F12+F14,2)</f>
-        <v>1088.3</v>
+        <v>988.3</v>
       </c>
       <c r="G15" s="12">
         <f>ROUND(G7+G8+G9+G12+G14,2)</f>
-        <v>1088.3</v>
+        <v>988.3</v>
       </c>
       <c r="H15" s="12">
         <f>ROUND(H7+H8+H9+H10+H12+H14,2)</f>
-        <v>1172.69</v>
+        <v>1072.69</v>
       </c>
       <c r="I15" s="12">
         <f>ROUND(I7+I8+I9+I10+I12+I14,2)</f>
-        <v>1172.69</v>
+        <v>1072.69</v>
       </c>
       <c r="J15" s="12">
         <f>ROUND(J7+J8+J9+J12+J14,2)</f>
-        <v>1063.3</v>
+        <v>963.3</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1270,31 +1270,31 @@
       <c r="C16" s="25"/>
       <c r="D16" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="E16" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>876.3</v>
+        <v>776.3</v>
       </c>
       <c r="F16" s="12">
         <f>ROUND(F7+F8+F9+F13+F14,2)</f>
-        <v>1296.8499999999999</v>
+        <v>1196.8499999999999</v>
       </c>
       <c r="G16" s="12">
         <f>ROUND(G7+G8+G9+G13+G14,2)</f>
-        <v>1296.8499999999999</v>
+        <v>1196.8499999999999</v>
       </c>
       <c r="H16" s="12">
         <f>ROUND(H7+H8+H9+H10+H13+H14,2)</f>
-        <v>1381.24</v>
+        <v>1281.24</v>
       </c>
       <c r="I16" s="12">
         <f>ROUND(I7+I8+I9+I10+I13+I14,2)</f>
-        <v>1381.24</v>
+        <v>1281.24</v>
       </c>
       <c r="J16" s="12">
         <f>ROUND(J7+J8+J9+J13+J14,2)</f>
-        <v>1271.8499999999999</v>
+        <v>1171.8499999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1305,31 +1305,31 @@
       <c r="C17" s="25"/>
       <c r="D17" s="12">
         <f t="shared" ref="D17:J18" si="0">ROUND(D15*0.13,2)</f>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="E17" s="12">
         <f t="shared" si="0"/>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="0"/>
-        <v>141.47999999999999</v>
+        <v>128.47999999999999</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>141.47999999999999</v>
+        <v>128.47999999999999</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>152.44999999999999</v>
+        <v>139.44999999999999</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" si="0"/>
-        <v>152.44999999999999</v>
+        <v>139.44999999999999</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>138.22999999999999</v>
+        <v>125.23</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1340,31 +1340,31 @@
       <c r="C18" s="25"/>
       <c r="D18" s="12">
         <f t="shared" si="0"/>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="E18" s="12">
         <f t="shared" si="0"/>
-        <v>113.92</v>
+        <v>100.92</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="0"/>
-        <v>168.59</v>
+        <v>155.59</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="0"/>
-        <v>168.59</v>
+        <v>155.59</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>179.56</v>
+        <v>166.56</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" si="0"/>
-        <v>179.56</v>
+        <v>166.56</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>165.34</v>
+        <v>152.34</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1375,31 +1375,31 @@
       <c r="C19" s="25"/>
       <c r="D19" s="13">
         <f t="shared" ref="D19:J19" si="1">D15+D17</f>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="E19" s="13">
         <f t="shared" si="1"/>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="1"/>
-        <v>1229.78</v>
+        <v>1116.78</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="1"/>
-        <v>1229.78</v>
+        <v>1116.78</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>1325.14</v>
+        <v>1212.1400000000001</v>
       </c>
       <c r="I19" s="13">
         <f t="shared" si="1"/>
-        <v>1325.14</v>
+        <v>1212.1400000000001</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v>1201.53</v>
+        <v>1088.53</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1410,31 +1410,31 @@
       <c r="C20" s="25"/>
       <c r="D20" s="14">
         <f>D19</f>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="E20" s="14">
         <f>E19</f>
-        <v>990.21999999999991</v>
+        <v>877.21999999999991</v>
       </c>
       <c r="F20" s="14">
         <f>F16+F18</f>
-        <v>1465.4399999999998</v>
+        <v>1352.4399999999998</v>
       </c>
       <c r="G20" s="14">
         <f>G16+G18</f>
-        <v>1465.4399999999998</v>
+        <v>1352.4399999999998</v>
       </c>
       <c r="H20" s="14">
         <f>H16+H18</f>
-        <v>1560.8</v>
+        <v>1447.8</v>
       </c>
       <c r="I20" s="14">
         <f>I16+I18</f>
-        <v>1560.8</v>
+        <v>1447.8</v>
       </c>
       <c r="J20" s="14">
         <f>J16+J18</f>
-        <v>1437.1899999999998</v>
+        <v>1324.1899999999998</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1556,31 +1556,31 @@
       <c r="C27" s="25"/>
       <c r="D27" s="13">
         <f t="shared" ref="D27:J27" si="2">ROUND(D24*D25+D26-D19,2)</f>
-        <v>243.78</v>
+        <v>356.78</v>
       </c>
       <c r="E27" s="13">
         <f t="shared" si="2"/>
-        <v>58.78</v>
+        <v>171.78</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="2"/>
-        <v>449.22</v>
+        <v>562.22</v>
       </c>
       <c r="G27" s="13">
         <f t="shared" si="2"/>
-        <v>219.22</v>
+        <v>332.22</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="2"/>
-        <v>585.86</v>
+        <v>698.86</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="2"/>
-        <v>313.86</v>
+        <v>426.86</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="2"/>
-        <v>52.47</v>
+        <v>165.47</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1591,31 +1591,31 @@
       <c r="C28" s="25"/>
       <c r="D28" s="14">
         <f t="shared" ref="D28:J28" si="3">ROUND(D24*D25+D26-D20,2)</f>
-        <v>243.78</v>
+        <v>356.78</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="3"/>
-        <v>58.78</v>
+        <v>171.78</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>213.56</v>
+        <v>326.56</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="3"/>
-        <v>-16.440000000000001</v>
+        <v>96.56</v>
       </c>
       <c r="H28" s="14">
         <f t="shared" si="3"/>
-        <v>350.2</v>
+        <v>463.2</v>
       </c>
       <c r="I28" s="14">
         <f t="shared" si="3"/>
-        <v>78.2</v>
+        <v>191.2</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="3"/>
-        <v>-183.19</v>
+        <v>-70.19</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/AlertPro-Pricing-Template-v2.xlsx
+++ b/AlertPro-Pricing-Template-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50986D0-06B0-467E-ADB6-74EAB5DFBCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E8F8ED-C2E9-4D21-9F2B-2FED10F283FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1001,28 +1001,28 @@
         <v>850</v>
       </c>
       <c r="C7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="D7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="E7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="F7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="G7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="H7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="I7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
       <c r="J7" s="9">
-        <v>433.25</v>
+        <v>533.25</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1235,31 +1235,31 @@
       <c r="C15" s="25"/>
       <c r="D15" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="E15" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="F15" s="12">
         <f>ROUND(F7+F8+F9+F12+F14,2)</f>
-        <v>988.3</v>
+        <v>1088.3</v>
       </c>
       <c r="G15" s="12">
         <f>ROUND(G7+G8+G9+G12+G14,2)</f>
-        <v>988.3</v>
+        <v>1088.3</v>
       </c>
       <c r="H15" s="12">
         <f>ROUND(H7+H8+H9+H10+H12+H14,2)</f>
-        <v>1072.69</v>
+        <v>1172.69</v>
       </c>
       <c r="I15" s="12">
         <f>ROUND(I7+I8+I9+I10+I12+I14,2)</f>
-        <v>1072.69</v>
+        <v>1172.69</v>
       </c>
       <c r="J15" s="12">
         <f>ROUND(J7+J8+J9+J12+J14,2)</f>
-        <v>963.3</v>
+        <v>1063.3</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1270,31 +1270,31 @@
       <c r="C16" s="25"/>
       <c r="D16" s="12">
         <f>ROUND(D7+D8+D9+D14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="E16" s="12">
         <f>ROUND(E7+E8+E9+E14,2)</f>
-        <v>776.3</v>
+        <v>876.3</v>
       </c>
       <c r="F16" s="12">
         <f>ROUND(F7+F8+F9+F13+F14,2)</f>
-        <v>1196.8499999999999</v>
+        <v>1296.8499999999999</v>
       </c>
       <c r="G16" s="12">
         <f>ROUND(G7+G8+G9+G13+G14,2)</f>
-        <v>1196.8499999999999</v>
+        <v>1296.8499999999999</v>
       </c>
       <c r="H16" s="12">
         <f>ROUND(H7+H8+H9+H10+H13+H14,2)</f>
-        <v>1281.24</v>
+        <v>1381.24</v>
       </c>
       <c r="I16" s="12">
         <f>ROUND(I7+I8+I9+I10+I13+I14,2)</f>
-        <v>1281.24</v>
+        <v>1381.24</v>
       </c>
       <c r="J16" s="12">
         <f>ROUND(J7+J8+J9+J13+J14,2)</f>
-        <v>1171.8499999999999</v>
+        <v>1271.8499999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1305,31 +1305,31 @@
       <c r="C17" s="25"/>
       <c r="D17" s="12">
         <f t="shared" ref="D17:J18" si="0">ROUND(D15*0.13,2)</f>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="E17" s="12">
         <f t="shared" si="0"/>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="0"/>
-        <v>128.47999999999999</v>
+        <v>141.47999999999999</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>128.47999999999999</v>
+        <v>141.47999999999999</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="0"/>
-        <v>139.44999999999999</v>
+        <v>152.44999999999999</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" si="0"/>
-        <v>139.44999999999999</v>
+        <v>152.44999999999999</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="0"/>
-        <v>125.23</v>
+        <v>138.22999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1340,31 +1340,31 @@
       <c r="C18" s="25"/>
       <c r="D18" s="12">
         <f t="shared" si="0"/>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="E18" s="12">
         <f t="shared" si="0"/>
-        <v>100.92</v>
+        <v>113.92</v>
       </c>
       <c r="F18" s="12">
         <f t="shared" si="0"/>
-        <v>155.59</v>
+        <v>168.59</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="0"/>
-        <v>155.59</v>
+        <v>168.59</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="0"/>
-        <v>166.56</v>
+        <v>179.56</v>
       </c>
       <c r="I18" s="12">
         <f t="shared" si="0"/>
-        <v>166.56</v>
+        <v>179.56</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="0"/>
-        <v>152.34</v>
+        <v>165.34</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1375,31 +1375,31 @@
       <c r="C19" s="25"/>
       <c r="D19" s="13">
         <f t="shared" ref="D19:J19" si="1">D15+D17</f>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="E19" s="13">
         <f t="shared" si="1"/>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="1"/>
-        <v>1116.78</v>
+        <v>1229.78</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="1"/>
-        <v>1116.78</v>
+        <v>1229.78</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>1212.1400000000001</v>
+        <v>1325.14</v>
       </c>
       <c r="I19" s="13">
         <f t="shared" si="1"/>
-        <v>1212.1400000000001</v>
+        <v>1325.14</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v>1088.53</v>
+        <v>1201.53</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1410,31 +1410,31 @@
       <c r="C20" s="25"/>
       <c r="D20" s="14">
         <f>D19</f>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="E20" s="14">
         <f>E19</f>
-        <v>877.21999999999991</v>
+        <v>990.21999999999991</v>
       </c>
       <c r="F20" s="14">
         <f>F16+F18</f>
-        <v>1352.4399999999998</v>
+        <v>1465.4399999999998</v>
       </c>
       <c r="G20" s="14">
         <f>G16+G18</f>
-        <v>1352.4399999999998</v>
+        <v>1465.4399999999998</v>
       </c>
       <c r="H20" s="14">
         <f>H16+H18</f>
-        <v>1447.8</v>
+        <v>1560.8</v>
       </c>
       <c r="I20" s="14">
         <f>I16+I18</f>
-        <v>1447.8</v>
+        <v>1560.8</v>
       </c>
       <c r="J20" s="14">
         <f>J16+J18</f>
-        <v>1324.1899999999998</v>
+        <v>1437.1899999999998</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1556,31 +1556,31 @@
       <c r="C27" s="25"/>
       <c r="D27" s="13">
         <f t="shared" ref="D27:J27" si="2">ROUND(D24*D25+D26-D19,2)</f>
-        <v>356.78</v>
+        <v>243.78</v>
       </c>
       <c r="E27" s="13">
         <f t="shared" si="2"/>
-        <v>171.78</v>
+        <v>58.78</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="2"/>
-        <v>562.22</v>
+        <v>449.22</v>
       </c>
       <c r="G27" s="13">
         <f t="shared" si="2"/>
-        <v>332.22</v>
+        <v>219.22</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="2"/>
-        <v>698.86</v>
+        <v>585.86</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="2"/>
-        <v>426.86</v>
+        <v>313.86</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="2"/>
-        <v>165.47</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -1591,31 +1591,31 @@
       <c r="C28" s="25"/>
       <c r="D28" s="14">
         <f t="shared" ref="D28:J28" si="3">ROUND(D24*D25+D26-D20,2)</f>
-        <v>356.78</v>
+        <v>243.78</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="3"/>
-        <v>171.78</v>
+        <v>58.78</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>326.56</v>
+        <v>213.56</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="3"/>
-        <v>96.56</v>
+        <v>-16.440000000000001</v>
       </c>
       <c r="H28" s="14">
         <f t="shared" si="3"/>
-        <v>463.2</v>
+        <v>350.2</v>
       </c>
       <c r="I28" s="14">
         <f t="shared" si="3"/>
-        <v>191.2</v>
+        <v>78.2</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="3"/>
-        <v>-70.19</v>
+        <v>-183.19</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="6.05" customHeight="1" x14ac:dyDescent="0.3"/>
